--- a/raw/ph_food_economy_raw.xlsx
+++ b/raw/ph_food_economy_raw.xlsx
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24T16:26:57+00:00</t>
+          <t>2026-10-25T18:22:22+00:00</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nwpc.dole.gov.ph/regionandwages/current-real-minimum-wage-rates/</t>
+          <t>https://www.pna.gov.ph/articles/1227990</t>
         </is>
       </c>
     </row>
@@ -20045,7 +20045,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -20055,7 +20055,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.da.gov.ph/rice-import-ban-lifts-palay-prices-nationwide/</t>
+          <t>https://portcalls.com/marcos-issues-eo-62-modifying-import-tariffs-including-on-rice</t>
         </is>
       </c>
     </row>
@@ -20067,12 +20067,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Imports of regular and well-milled rice suspended</t>
+          <t>Imports of regular and well-milled rice suspended (EO 93)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.da.gov.ph/rice-import-ban-lifts-palay-prices-nationwide/</t>
+          <t>https://portcalls.com/ph-rice-import-ban-extended-to-end-2025/</t>
         </is>
       </c>
     </row>
@@ -20084,7 +20084,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Price-indexed rice tariff (15-35%) starts; imports resume</t>
+          <t>Price-indexed rice tariff (15-35%) starts; imports resume (EO 105)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/raw/ph_food_economy_raw.xlsx
+++ b/raw/ph_food_economy_raw.xlsx
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25T18:22:22+00:00</t>
+          <t>2026-10-26T22:26:35+00:00</t>
         </is>
       </c>
     </row>
@@ -17907,7 +17907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19716,6 +19716,60 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>70.6737</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PROVISIONAL: average of ECB daily reference rates to 2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1.1214</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PROVISIONAL: average of ECB daily reference rates to 2026-10-26</t>
         </is>
       </c>
     </row>

--- a/raw/ph_food_economy_raw.xlsx
+++ b/raw/ph_food_economy_raw.xlsx
@@ -11,12 +11,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="psa_inflation" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="psa_peso_power" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="psa_gdp_growth" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ecb_fx" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sws_hunger" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ncr_min_wage" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rice_policy_events" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region_lookup" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="about" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ecb_fx_daily" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ecb_fx" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sws_hunger" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ncr_min_wage" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rice_policy_events" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region_lookup" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="about" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4576,6 +4577,560 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>region_key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>island_group</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rice_label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cpi_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PHILIPPINES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NCR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NCR - National Capital Region</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>National Capital Region (NCR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CAR - Cordillera Administrative Region</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cordillera Administrative Region (CAR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ilocos</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>I - Ilocos Region</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Region I (Ilocos Region)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cagayan Valley</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>II - Cagayan Valley</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Region II (Cagayan Valley)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Central Luzon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>III - Central Luzon</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Region III (Central Luzon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R4A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CALABARZON</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IV-A - CALABARZON</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Region IV-A (CALABARZON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R4B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MIMAROPA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MIMAROPA Region</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MIMAROPA Region</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bicol</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>V - Bicol Region</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Region V (Bicol Region)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Western Visayas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VI - Western Visayas</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Region VI (Western Visayas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NIR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Negros Island</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Negros Island Region (NIR)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Negros Island Region (NIR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Central Visayas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VII - Central Visayas</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Region VII (Central Visayas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R08</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Eastern Visayas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VIII - Eastern Visayas</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Region VIII (Eastern Visayas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Zamboanga Peninsula</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>IX - Zamboanga Peninsula</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Region IX (Zamboanga Peninsula)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Northern Mindanao</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>X - Northern Mindanao</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Region X (Northern Mindanao)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Davao</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>XI - Davao Region</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Region XI (Davao Region)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SOCCSKSARGEN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>XII - SOCCSKSARGEN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Region XII (SOCCSKSARGEN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Caraga</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>XIII - Caraga</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Region XIII (Caraga)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BARMM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BARMM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BARMM - Bangsamoro Autonomous Region in Muslim Mindanao</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bangsamoro Autonomous Region in Muslim Mindanao (BARMM)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -4599,7 +5154,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26T22:26:35+00:00</t>
+          <t>2026-10-26T22:28:21+00:00</t>
         </is>
       </c>
     </row>
@@ -17907,7 +18462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17950,12 +18505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61.0896363636364</t>
+          <t>70.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17977,12 +18532,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60.4860952380952</t>
+          <t>70.265</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -18004,12 +18559,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60.73565</t>
+          <t>70.219</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -18031,12 +18586,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>61.1712857142857</t>
+          <t>70.702</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -18058,12 +18613,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>62.5230909090909</t>
+          <t>70.203</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -18085,12 +18640,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>63.17705</t>
+          <t>70.475</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -18112,12 +18667,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>63.4161304347826</t>
+          <t>70.397</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -18139,12 +18694,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>62.7102272727273</t>
+          <t>70.169</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -18166,12 +18721,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>62.2557619047619</t>
+          <t>70.225</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -18193,12 +18748,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>62.6549565217391</t>
+          <t>70.393</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -18220,12 +18775,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>62.4095238095238</t>
+          <t>70.693</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -18247,12 +18802,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>61.20305</t>
+          <t>70.858</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -18274,12 +18829,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>60.4789545454545</t>
+          <t>70.715</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -18301,12 +18856,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>60.4426</t>
+          <t>70.804</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -18328,12 +18883,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>62.0128571428572</t>
+          <t>71.121</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -18355,12 +18910,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>63.74359999999998</t>
+          <t>71.162</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -18382,12 +18937,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>62.74157142857143</t>
+          <t>71.235</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -18409,12 +18964,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>64.90076190476191</t>
+          <t>71.54</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -18426,7 +18981,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -18436,24 +18991,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>66.41452173913041</t>
+          <t>1.1298</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -18463,24 +19018,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>66.45223809523809</t>
+          <t>1.1225</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -18490,24 +19045,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>67.2118181818182</t>
+          <t>1.1204</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -18517,24 +19072,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>67.88434782608697</t>
+          <t>1.1269</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -18544,24 +19099,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>68.06590000000001</t>
+          <t>1.1177</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -18571,24 +19126,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>68.94142857142857</t>
+          <t>1.1186</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -18598,24 +19153,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>69.4792380952381</t>
+          <t>1.1206</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -18625,24 +19180,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>68.7902</t>
+          <t>1.1181</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -18652,24 +19207,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>68.87386363636364</t>
+          <t>1.1188</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -18679,24 +19234,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>70.6087</t>
+          <t>1.1195</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -18706,24 +19261,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>71.64955</t>
+          <t>1.1208</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -18733,24 +19288,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>70.46236363636363</t>
+          <t>1.1253</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -18760,24 +19315,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>70.33547826086956</t>
+          <t>1.1225</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -18787,24 +19342,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>71.2357142857143</t>
+          <t>1.1215</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -18814,17 +19369,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>72.09740909090908</t>
+          <t>1.1234</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Philippine peso/Euro ECB reference exchange rate</t>
+          <t>US dollar/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
@@ -18841,12 +19396,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.0905136363636</t>
+          <t>1.1205</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -18868,12 +19423,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.0794714285714</t>
+          <t>1.1193</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -18895,881 +19450,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.08722</t>
+          <t>1.1188</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1.0727761904762</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1.0812227272727</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1.0759</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1.0844086956522</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1.1012181818182</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1.1106</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2024-10</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1.0904347826087</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1.0630142857143</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1.047875</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1.0353727272727</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>1.04125</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1.080680952381</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>1.1213950000000001</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1.1278047619047618</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>1.1516190476190478</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>1.1676869565217392</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>1.1631428571428575</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1.1732227272727274</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1.1630434782608696</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1.15602</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>1.1708714285714283</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1.1738238095238096</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1.182395</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1.1558318181818181</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1.1706400000000001</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1.16732</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>1.1518</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1.1417478260869562</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>1.1593095238095241</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1.1513227272727276</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>US dollar/Euro ECB reference exchange rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>PHP</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>70.6737</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>PROVISIONAL: average of ECB daily reference rates to 2026-10-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1.1214</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>PROVISIONAL: average of ECB daily reference rates to 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19784,168 +19475,1869 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>CURRENCY</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>fieldwork_start</t>
+          <t>CURRENCY_DENOM</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>hunger_pct</t>
+          <t>TIME_PERIOD</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>OBS_VALUE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TITLE</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mar 2025</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>27.2</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.gmanetwork.com/news/topstories/nation/941035/hunger-survey-sws-march-2025/story/</t>
+          <t>61.0896363636364</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jun 2025</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>16.1</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.philstar.com/headlines/2025/08/16/2465924/hunger-among-filipino-families-drops-161-june-sws</t>
+          <t>60.4860952380952</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sep 2025</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>22</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.bworldonline.com/the-nation/2025/11/05/710365/hunger-rises-to-22-in-q3-sws/</t>
+          <t>60.73565</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nov 2025</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>20.1</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://mb.com.ph/2026/01/14/hunger-incidence-among-filipino-families-eases-in-q4-2025-sws</t>
+          <t>61.1712857142857</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>23.2</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://newsinfo.inquirer.net/2227801/sws-hunger-among-filipino-families-rises-to-23-2-in-march-2026</t>
+          <t>62.5230909090909</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>20.3</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.philstar.com/headlines/2026/08/26/2551864/hunger-slightly-down-203-sws</t>
+          <t>63.17705</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>22.6</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.gmanetwork.com/news/topstories/nation/1005905/more-filipino-families-experienced-hunger-in-3q-of-2026-sws-report/story/</t>
+          <t>63.4161304347826</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>62.7102272727273</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>62.2557619047619</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>62.6549565217391</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>62.4095238095238</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>61.20305</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>60.4789545454545</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>60.4426</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>62.0128571428572</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>63.74359999999998</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>62.74157142857143</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>64.90076190476191</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>66.41452173913041</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>66.45223809523809</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>67.2118181818182</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>67.88434782608697</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>68.06590000000001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>68.94142857142857</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>69.4792380952381</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>68.7902</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>68.87386363636364</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>70.6087</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>71.64955</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>70.46236363636363</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>70.33547826086956</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>71.2357142857143</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>72.09740909090908</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Philippine peso/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.0905136363636</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1.0794714285714</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1.08722</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1.0727761904762</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.0812227272727</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.0759</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.0844086956522</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.1012181818182</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.1106</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.0904347826087</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.0630142857143</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.047875</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.0353727272727</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1.04125</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1.080680952381</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.1213950000000001</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.1278047619047618</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.1516190476190478</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.1676869565217392</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.1631428571428575</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.1732227272727274</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1.1630434782608696</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.15602</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1.1708714285714283</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1.1738238095238096</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.182395</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.1558318181818181</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.1706400000000001</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.16732</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1.1518</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.1417478260869562</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.1593095238095241</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.1513227272727276</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>US dollar/Euro ECB reference exchange rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>70.6737</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PROVISIONAL: average of ECB daily reference rates to 2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1.1214</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PROVISIONAL: average of ECB daily reference rates to 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19960,23 +21352,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>wage_order</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>fieldwork_start</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>daily_wage_php</t>
+          <t>hunger_pct</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -19988,80 +21380,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Wage Order NCR-24</t>
+          <t>Mar 2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>610</v>
+        <v>27.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://nwpc.dole.gov.ph/regionandwages/current-real-minimum-wage-rates/</t>
+          <t>https://www.gmanetwork.com/news/topstories/nation/941035/hunger-survey-sws-march-2025/story/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wage Order NCR-25</t>
+          <t>Jun 2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>645</v>
+        <v>16.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pna.gov.ph/articles/1227990</t>
+          <t>https://www.philstar.com/headlines/2025/08/16/2465924/hunger-among-filipino-families-drops-161-june-sws</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wage Order NCR-26</t>
+          <t>Sep 2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>695</v>
+        <v>22</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.sunstar.com.ph/manila/ncr-wage-hike-starts-july-25</t>
+          <t>https://www.bworldonline.com/the-nation/2025/11/05/710365/hunger-rises-to-22-in-q3-sws/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wage Order NCR-28</t>
+          <t>Nov 2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>755</v>
+        <v>20.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.gmanetwork.com/news/money/economy/1003769/dole-p60-wage-hike-in-ncr-takes-effect-sept-26/story/</t>
+          <t>https://mb.com.ph/2026/01/14/hunger-incidence-among-filipino-families-eases-in-q4-2025-sws</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://newsinfo.inquirer.net/2227801/sws-hunger-among-filipino-families-rises-to-23-2-in-march-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.philstar.com/headlines/2026/08/26/2551864/hunger-slightly-down-203-sws</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.gmanetwork.com/news/topstories/nation/1005905/more-filipino-families-experienced-hunger-in-3q-of-2026-sws-report/story/</t>
         </is>
       </c>
     </row>
@@ -20076,21 +21528,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>wage_order</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>effective_date</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
+        <is>
+          <t>daily_wage_php</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -20099,51 +21556,80 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>Wage Order NCR-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rice import tariff cut from 35% to 15% (EO 62)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://portcalls.com/marcos-issues-eo-62-modifying-import-tariffs-including-on-rice</t>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>610</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nwpc.dole.gov.ph/regionandwages/current-real-minimum-wage-rates/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>Wage Order NCR-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Imports of regular and well-milled rice suspended (EO 93)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://portcalls.com/ph-rice-import-ban-extended-to-end-2025/</t>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>645</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.pna.gov.ph/articles/1227990</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>Wage Order NCR-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Price-indexed rice tariff (15-35%) starts; imports resume (EO 105)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.fas.usda.gov/data/gain/2026/02/philippines-philippines-implements-quarterly-rice-import-tariff-adjustment-based-international</t>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>695</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.sunstar.com.ph/manila/ncr-wage-hike-starts-july-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Wage Order NCR-28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>755</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.gmanetwork.com/news/money/economy/1003769/dole-p60-wage-hike-in-ncr-takes-effect-sept-26/story/</t>
         </is>
       </c>
     </row>
@@ -20158,546 +21644,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>region_key</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>island_group</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>rice_label</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>cpi_label</t>
+          <t>source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Rice import tariff cut from 35% to 15% (EO 62)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>National</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PHILIPPINES</t>
+          <t>https://portcalls.com/marcos-issues-eo-62-modifying-import-tariffs-including-on-rice</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NCR</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NCR</t>
+          <t>Imports of regular and well-milled rice suspended (EO 93)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NCR - National Capital Region</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>National Capital Region (NCR)</t>
+          <t>https://portcalls.com/ph-rice-import-ban-extended-to-end-2025/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>Price-indexed rice tariff (15-35%) starts; imports resume (EO 105)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CAR - Cordillera Administrative Region</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Cordillera Administrative Region (CAR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ilocos</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>I - Ilocos Region</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Region I (Ilocos Region)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cagayan Valley</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>II - Cagayan Valley</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Region II (Cagayan Valley)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>R03</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Central Luzon</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>III - Central Luzon</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Region III (Central Luzon)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>R4A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CALABARZON</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IV-A - CALABARZON</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Region IV-A (CALABARZON)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>R4B</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MIMAROPA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MIMAROPA Region</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIMAROPA Region</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>R05</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Bicol</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>V - Bicol Region</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Region V (Bicol Region)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>R06</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Western Visayas</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visayas</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>VI - Western Visayas</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Region VI (Western Visayas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NIR</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Negros Island</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visayas</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Negros Island Region (NIR)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Negros Island Region (NIR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>R07</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Central Visayas</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visayas</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VII - Central Visayas</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Region VII (Central Visayas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>R08</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Eastern Visayas</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visayas</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VIII - Eastern Visayas</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Region VIII (Eastern Visayas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>R09</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Zamboanga Peninsula</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>IX - Zamboanga Peninsula</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Region IX (Zamboanga Peninsula)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Northern Mindanao</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>X - Northern Mindanao</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Region X (Northern Mindanao)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Davao</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>XI - Davao Region</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Region XI (Davao Region)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SOCCSKSARGEN</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>XII - SOCCSKSARGEN</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Region XII (SOCCSKSARGEN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Caraga</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>XIII - Caraga</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Region XIII (Caraga)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BARMM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BARMM</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>BARMM - Bangsamoro Autonomous Region in Muslim Mindanao</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Bangsamoro Autonomous Region in Muslim Mindanao (BARMM)</t>
+          <t>https://www.fas.usda.gov/data/gain/2026/02/philippines-philippines-implements-quarterly-rice-import-tariff-adjustment-based-international</t>
         </is>
       </c>
     </row>

--- a/raw/ph_food_economy_raw.xlsx
+++ b/raw/ph_food_economy_raw.xlsx
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26T22:28:21+00:00</t>
+          <t>2026-10-26T22:29:18+00:00</t>
         </is>
       </c>
     </row>

--- a/raw/ph_food_economy_raw.xlsx
+++ b/raw/ph_food_economy_raw.xlsx
@@ -16,8 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sws_hunger" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ncr_min_wage" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rice_policy_events" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region_lookup" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="about" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bsp_outlook" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="region_lookup" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="about" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4577,546 +4578,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>region_key</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>item</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>island_group</t>
+          <t>value</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>rice_label</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>cpi_label</t>
+          <t>source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>National</t>
-        </is>
+          <t>policy_rate_pct</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PHILIPPINES</t>
+          <t>https://www.manilatimes.net/2026/10/27/business/top-business/inflation-threatens-prolonged-tightening/2454325</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NCR</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NCR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
+          <t>inflation_forecast_2026_pct</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NCR - National Capital Region</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>National Capital Region (NCR)</t>
+          <t>https://www.manilatimes.net/2026/10/27/business/top-business/inflation-threatens-prolonged-tightening/2454325</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
+          <t>inflation_forecast_2027_pct</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAR - Cordillera Administrative Region</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Cordillera Administrative Region (CAR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ilocos</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>I - Ilocos Region</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Region I (Ilocos Region)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cagayan Valley</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>II - Cagayan Valley</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Region II (Cagayan Valley)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>R03</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Central Luzon</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>III - Central Luzon</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Region III (Central Luzon)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>R4A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CALABARZON</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IV-A - CALABARZON</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Region IV-A (CALABARZON)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>R4B</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MIMAROPA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MIMAROPA Region</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIMAROPA Region</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>R05</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Bicol</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Luzon</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>V - Bicol Region</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Region V (Bicol Region)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>R06</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Western Visayas</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Visayas</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>VI - Western Visayas</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Region VI (Western Visayas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NIR</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Negros Island</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Visayas</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Negros Island Region (NIR)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Negros Island Region (NIR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>R07</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Central Visayas</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Visayas</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VII - Central Visayas</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Region VII (Central Visayas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>R08</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Eastern Visayas</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Visayas</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VIII - Eastern Visayas</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Region VIII (Eastern Visayas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>R09</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Zamboanga Peninsula</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>IX - Zamboanga Peninsula</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Region IX (Zamboanga Peninsula)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Northern Mindanao</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>X - Northern Mindanao</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Region X (Northern Mindanao)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Davao</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>XI - Davao Region</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Region XI (Davao Region)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SOCCSKSARGEN</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>XII - SOCCSKSARGEN</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Region XII (SOCCSKSARGEN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Caraga</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>XIII - Caraga</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Region XIII (Caraga)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BARMM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BARMM</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Mindanao</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>BARMM - Bangsamoro Autonomous Region in Muslim Mindanao</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Bangsamoro Autonomous Region in Muslim Mindanao (BARMM)</t>
+          <t>https://www.manilatimes.net/2026/10/27/business/top-business/inflation-threatens-prolonged-tightening/2454325</t>
         </is>
       </c>
     </row>
@@ -5131,6 +4674,560 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>region_key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>island_group</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rice_label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cpi_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PHILIPPINES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NCR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NCR - National Capital Region</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>National Capital Region (NCR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CAR - Cordillera Administrative Region</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cordillera Administrative Region (CAR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ilocos</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>I - Ilocos Region</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Region I (Ilocos Region)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cagayan Valley</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>II - Cagayan Valley</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Region II (Cagayan Valley)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Central Luzon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>III - Central Luzon</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Region III (Central Luzon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R4A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CALABARZON</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IV-A - CALABARZON</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Region IV-A (CALABARZON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R4B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MIMAROPA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MIMAROPA Region</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MIMAROPA Region</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bicol</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Luzon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>V - Bicol Region</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Region V (Bicol Region)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Western Visayas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VI - Western Visayas</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Region VI (Western Visayas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NIR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Negros Island</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Negros Island Region (NIR)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Negros Island Region (NIR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Central Visayas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VII - Central Visayas</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Region VII (Central Visayas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R08</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Eastern Visayas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Visayas</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VIII - Eastern Visayas</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Region VIII (Eastern Visayas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Zamboanga Peninsula</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>IX - Zamboanga Peninsula</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Region IX (Zamboanga Peninsula)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Northern Mindanao</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>X - Northern Mindanao</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Region X (Northern Mindanao)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Davao</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>XI - Davao Region</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Region XI (Davao Region)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SOCCSKSARGEN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>XII - SOCCSKSARGEN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Region XII (SOCCSKSARGEN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Caraga</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>XIII - Caraga</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Region XIII (Caraga)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BARMM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BARMM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mindanao</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BARMM - Bangsamoro Autonomous Region in Muslim Mindanao</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Bangsamoro Autonomous Region in Muslim Mindanao (BARMM)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -5154,7 +5251,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26T22:29:18+00:00</t>
+          <t>2026-10-27T04:54:45+00:00</t>
         </is>
       </c>
     </row>
